--- a/data/predictions/2026-03-29_ST.xlsx
+++ b/data/predictions/2026-03-29_ST.xlsx
@@ -541,12 +541,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -558,8 +562,10 @@
           <t>DOUBLE SHOW</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -576,47 +582,79 @@
           <t>12/2/1/12/5/2</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5.736842105263158</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.716</v>
-      </c>
-      <c r="R2" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.5</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5.736842105263158</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5.716</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -628,8 +666,10 @@
           <t>MY FLYING ANGEL</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>12</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -646,47 +686,79 @@
           <t>6/4/5/4/5/3</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.5258</v>
-      </c>
-      <c r="R3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.6</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5.5258</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -698,8 +770,10 @@
           <t>BLING BLING GENIUS</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>6</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -716,47 +790,79 @@
           <t>4/12/5/2/7/5</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>8.578947368421051</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.4641</v>
-      </c>
-      <c r="R4" t="n">
-        <v>12</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7.1</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>8.578947368421051</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5.4641</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -768,8 +874,10 @@
           <t>ACE</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>5</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -786,47 +894,79 @@
           <t>8/6/4/10/5/8</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>10</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.1114</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10.1</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.1114</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -838,8 +978,10 @@
           <t>STRATHPEFFER</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>11</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -856,47 +998,79 @@
           <t>14/2/2/1/5/3</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>8.3125</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6.1035</v>
-      </c>
-      <c r="R6" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.9</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>8.3125</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>6.1035</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -908,8 +1082,10 @@
           <t>APOLAR FIGHTER</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>3</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -926,47 +1102,79 @@
           <t>10/14/1/2/1/8</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.6875</v>
-      </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.4633</v>
-      </c>
-      <c r="R7" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7.5</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2.6875</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5.4633</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -978,8 +1186,10 @@
           <t>VIEW OF COSMOS</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>13</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -996,47 +1206,79 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.2279</v>
-      </c>
-      <c r="R8" t="n">
-        <v>9</v>
-      </c>
-      <c r="S8" t="n">
-        <v>9.4</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6.625</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5.2279</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1048,8 +1290,10 @@
           <t>SHOTGUN</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>10</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1066,47 +1310,79 @@
           <t>2/3/1/2/6/9</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.1317</v>
-      </c>
-      <c r="R9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10.4</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5.1317</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1118,8 +1394,10 @@
           <t>STORM RUNNER</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>4</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1136,47 +1414,79 @@
           <t>1/1/3/3/2/2</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6.684210526315789</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.4438</v>
-      </c>
-      <c r="R10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.2</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8.81</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6.684210526315789</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>6.4438</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1188,8 +1498,10 @@
           <t>DOUBLE WIN</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>9</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1206,47 +1518,79 @@
           <t>3/10/6/9/1/1</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>6.684210526315789</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.7753</v>
-      </c>
-      <c r="R11" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6.2</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>6.684210526315789</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5.7753</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1258,8 +1602,10 @@
           <t>STAR BROSE</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>2</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1276,47 +1622,79 @@
           <t>2/5/9/1/5/3</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="K12" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.421052631578947</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.5623</v>
-      </c>
-      <c r="R12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>7.7</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2.421052631578947</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5.5623</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1328,8 +1706,10 @@
           <t>SERANGOON</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>12</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1346,47 +1726,79 @@
           <t>7/1/12/4/7/3</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>7.631578947368421</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.4237</v>
-      </c>
-      <c r="R13" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S13" t="n">
-        <v>8.800000000000001</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>7.631578947368421</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5.4237</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1398,8 +1810,10 @@
           <t>AWESOME FLUKE</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,47 +1830,79 @@
           <t>6/1/11/6/2/1</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>8.071428571428571</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.1174</v>
-      </c>
-      <c r="R14" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.1</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>8.071428571428571</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6.1174</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1468,8 +1914,10 @@
           <t>MAX QUE</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>3</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1486,47 +1934,79 @@
           <t>3/2/1/3/3/3</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.9444</v>
-      </c>
-      <c r="R15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.9</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5.9444</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1538,8 +2018,10 @@
           <t>PACKING ANGEL</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>2</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1556,47 +2038,79 @@
           <t>8/4/10/3/4/1</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6.142857142857143</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.8368</v>
-      </c>
-      <c r="R16" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5.4</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6.62</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6.142857142857143</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5.8368</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>4</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1608,8 +2122,10 @@
           <t>JOY OF SPRING</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>4</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1626,47 +2142,79 @@
           <t>13/1/9/8/3/1</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="K17" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.571428571428572</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.5595</v>
-      </c>
-      <c r="R17" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>7.1</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3.571428571428572</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5.5595</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1678,8 +2226,10 @@
           <t>EVER LUCK</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>13</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1696,47 +2246,79 @@
           <t>7/3/2/1</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>10</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.4722</v>
-      </c>
-      <c r="R18" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.4</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6.4722</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1748,8 +2330,10 @@
           <t>PACKING PHOENIX</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>12</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1766,47 +2350,79 @@
           <t>8/3/5/1</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.0221</v>
-      </c>
-      <c r="R19" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6.9</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>6.0221</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1818,8 +2434,10 @@
           <t>GEORGIAN SIGMA</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>9</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1836,47 +2454,79 @@
           <t>4/2</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.0123</v>
-      </c>
-      <c r="R20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>7</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6.0123</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1888,8 +2538,10 @@
           <t>RUN RUN SUNRISE</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>5</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1906,47 +2558,79 @@
           <t>1/2/10</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="K21" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.5328</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>11.2</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5.17</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5.5328</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1958,8 +2642,10 @@
           <t>CIRCUIT FIERY</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>10</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1976,47 +2662,79 @@
           <t>1/2/3/1/4/2</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.3125</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.3492</v>
-      </c>
-      <c r="R22" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.3</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>8.3125</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6.3492</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2028,8 +2746,10 @@
           <t>NYX GLUCK</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>6</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2046,47 +2766,79 @@
           <t>10/4/3/5/1/3</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8.3125</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.1259</v>
-      </c>
-      <c r="R23" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.1</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>8.3125</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6.1259</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>3</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2098,8 +2850,10 @@
           <t>STATE SECURITY</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2116,47 +2870,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>6.0625</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.4028</v>
-      </c>
-      <c r="R24" t="n">
-        <v>10</v>
-      </c>
-      <c r="S24" t="n">
-        <v>8.5</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>6.0625</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5.4028</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2168,8 +2954,10 @@
           <t>ONE MORE</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>14</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2186,47 +2974,79 @@
           <t>9/6/5/3/10/7</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>10</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.1184</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>11.3</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5.1184</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>7</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2238,8 +3058,10 @@
           <t>VIGOR EYE</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2256,47 +3078,79 @@
           <t>9/3/4/3</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K26" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5.8674</v>
-      </c>
-      <c r="R26" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5.8</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>5.8674</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2308,8 +3162,10 @@
           <t>PRESTIGE EMPEROR</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>2</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2326,47 +3182,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>7.1875</v>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.4563</v>
-      </c>
-      <c r="R27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="S27" t="n">
-        <v>8.9</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>7.1875</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5.4563</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>3</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2378,8 +3266,10 @@
           <t>LIVE WIRE</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>5</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2396,47 +3286,79 @@
           <t>7/4/8/3</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="P28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5.4379</v>
-      </c>
-      <c r="R28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8.9</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>6.625</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>5.4379</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>4</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2448,8 +3370,10 @@
           <t>LIGHTNING ACE</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>4</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2466,47 +3390,79 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>7.1875</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.4122</v>
-      </c>
-      <c r="R29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="S29" t="n">
-        <v>9.199999999999999</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>7.1875</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>5.4122</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2518,8 +3474,10 @@
           <t>SALON S</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>11</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2536,47 +3494,79 @@
           <t>1/1/1</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>10</v>
-      </c>
-      <c r="K30" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>10</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.902</v>
-      </c>
-      <c r="R30" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.2</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>6.902</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>37.8</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2588,8 +3578,10 @@
           <t>LUCKY SAM GOR</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>3</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2606,47 +3598,79 @@
           <t>13/4/1/1/7/6</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="K31" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>9.357142857142858</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.8098</v>
-      </c>
-      <c r="R31" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="S31" t="n">
-        <v>6.7</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>9.357142857142858</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5.8098</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>3</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2658,8 +3682,10 @@
           <t>ALL'S WELL</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>9</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2676,47 +3702,79 @@
           <t>1/8/4/2/9/3</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>6</v>
-      </c>
-      <c r="K32" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.285714285714286</v>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.2798</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>11.3</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2.285714285714286</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5.2798</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2728,8 +3786,10 @@
           <t>URANUS STAR</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>12</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2746,47 +3806,79 @@
           <t>8/3/10/11/4/1</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K33" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>4.214285714285714</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.2125</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7</v>
-      </c>
-      <c r="S33" t="n">
-        <v>12.1</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>4.214285714285714</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>5.2125</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2798,8 +3890,10 @@
           <t>BULB GENERAL</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>7</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2816,47 +3910,79 @@
           <t>1/1/1/3</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K34" t="n">
-        <v>7</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.7476</v>
-      </c>
-      <c r="R34" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4.1</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>6.7476</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2868,8 +3994,10 @@
           <t>MAGNIFIQUE</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>6</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2886,47 +4014,79 @@
           <t>1/3/1/1/6/1</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="K35" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>8.3125</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.529</v>
-      </c>
-      <c r="R35" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5.1</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>8.3125</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>6.529</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>3</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2938,8 +4098,10 @@
           <t>PATCH OF STARS</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>2</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2956,47 +4118,79 @@
           <t>3/4/1/1/6/2</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="K36" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>8.875</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6.4433</v>
-      </c>
-      <c r="R36" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5.6</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>7.81</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>8.875</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>6.4433</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3008,8 +4202,10 @@
           <t>GALACTIC VOYAGE</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>4</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3026,47 +4222,79 @@
           <t>1/1/3/4</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K37" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>6.8125</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>6.4025</v>
-      </c>
-      <c r="R37" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5.8</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>6.8125</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>6.4025</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>10</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3078,8 +4306,10 @@
           <t>HAPPY INDEX</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>11</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3096,47 +4326,79 @@
           <t>2/1/3</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="K38" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>10</v>
-      </c>
-      <c r="P38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>6.5744</v>
-      </c>
-      <c r="R38" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.4</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>8.83</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>6.5744</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
       </c>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>10</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>2</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3148,8 +4410,10 @@
           <t>RISING FORCE</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>7</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3166,47 +4430,79 @@
           <t>2/2/1/7/2/1</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="K39" t="n">
-        <v>7</v>
-      </c>
-      <c r="L39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6.3112</v>
-      </c>
-      <c r="R39" t="n">
-        <v>15</v>
-      </c>
-      <c r="S39" t="n">
-        <v>5.7</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>8.29</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>6.3112</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
       </c>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>10</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
-        <v>3</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3218,8 +4514,10 @@
           <t>GENEVA</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>8</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3236,47 +4534,79 @@
           <t>3/5/6/1/2/6</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="K40" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>8</v>
-      </c>
-      <c r="P40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>5.866</v>
-      </c>
-      <c r="R40" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="S40" t="n">
-        <v>8.9</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6.62</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5.866</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
       </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>10</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>4</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3288,8 +4618,10 @@
           <t>PERFECTDAY</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>3</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3306,47 +4638,79 @@
           <t>5/9/2/1/1/7</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="K41" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>5</v>
-      </c>
-      <c r="P41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5.7988</v>
-      </c>
-      <c r="R41" t="n">
-        <v>9</v>
-      </c>
-      <c r="S41" t="n">
-        <v>9.4</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5.7988</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
       </c>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>11</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>1</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3358,8 +4722,10 @@
           <t>ENDUED</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>5</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3376,47 +4742,79 @@
           <t>1/3/4/6/1/2</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="K42" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>6.823529411764706</v>
-      </c>
-      <c r="P42" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>6.1546</v>
-      </c>
-      <c r="R42" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5.5</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>7.81</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>6.823529411764706</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>6.1546</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
       </c>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>11</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>2</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3428,8 +4826,10 @@
           <t>CHINA WIN</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3446,47 +4846,79 @@
           <t>2/1/1/2/6/4</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="K43" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>5.764705882352941</v>
-      </c>
-      <c r="P43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>5.9951</v>
-      </c>
-      <c r="R43" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S43" t="n">
-        <v>6.4</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5.764705882352941</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5.9951</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>11</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>3</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3498,8 +4930,10 @@
           <t>ANOTHER WORLD</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>11</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3516,47 +4950,79 @@
           <t>8/4/5/3/1/6</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="K44" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5</v>
-      </c>
-      <c r="O44" t="n">
-        <v>6.823529411764706</v>
-      </c>
-      <c r="P44" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="R44" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="S44" t="n">
-        <v>8.9</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6.823529411764706</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5.68</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
       </c>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>11</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
-        <v>4</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3568,8 +5034,10 @@
           <t>THE GOLDEN KNIGHT</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>3</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3586,39 +5054,67 @@
           <t>1/6/2/3/5/2</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="K45" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N45" t="n">
-        <v>5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>5.6784</v>
-      </c>
-      <c r="R45" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="S45" t="n">
-        <v>8.9</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7.43</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>5.6784</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
       </c>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3797,7 +5293,6 @@
           <t>1/1/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>10</v>
       </c>
@@ -3878,7 +5373,6 @@
           <t>13/4/1/1/7/6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.81</v>
       </c>
@@ -3959,7 +5453,6 @@
           <t>1/8/4/2/9/3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6</v>
       </c>
@@ -4040,7 +5533,6 @@
           <t>8/3/10/11/4/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.48</v>
       </c>
@@ -4121,7 +5613,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -4202,7 +5693,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -4283,7 +5773,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -4364,7 +5853,6 @@
           <t>7/4/8/6/5/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.52</v>
       </c>
@@ -4445,7 +5933,6 @@
           <t>3/10/9/5/2/12</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.14</v>
       </c>
@@ -4526,7 +6013,6 @@
           <t>4/11/3/8/10/8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.71</v>
       </c>
@@ -4607,7 +6093,6 @@
           <t>5/11/13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.67</v>
       </c>
@@ -4688,7 +6173,6 @@
           <t>8/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.33</v>
       </c>
@@ -4900,7 +6384,6 @@
           <t>1/1/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9.199999999999999</v>
       </c>
@@ -4981,7 +6464,6 @@
           <t>1/3/1/1/6/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>8.380000000000001</v>
       </c>
@@ -5062,7 +6544,6 @@
           <t>3/4/1/1/6/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.81</v>
       </c>
@@ -5228,7 +6709,6 @@
           <t>2/1/7/4/1/7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.19</v>
       </c>
@@ -5309,7 +6789,6 @@
           <t>7/11/11/5/1/7</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.57</v>
       </c>
@@ -5390,7 +6869,6 @@
           <t>7/6/13/7/5/4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.14</v>
       </c>
@@ -5471,7 +6949,6 @@
           <t>3/2/2/11/10/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.52</v>
       </c>
@@ -5552,7 +7029,6 @@
           <t>9/8/6/9/9/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.86</v>
       </c>
@@ -5718,7 +7194,6 @@
           <t>11/9/8/10/14/11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.24</v>
       </c>
@@ -5930,7 +7405,6 @@
           <t>2/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.83</v>
       </c>
@@ -6011,7 +7485,6 @@
           <t>2/2/1/7/2/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>8.289999999999999</v>
       </c>
@@ -6092,7 +7565,6 @@
           <t>3/5/6/1/2/6</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.62</v>
       </c>
@@ -6173,7 +7645,6 @@
           <t>5/9/2/1/1/7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.86</v>
       </c>
@@ -6254,7 +7725,6 @@
           <t>1/4/10/8/1/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.81</v>
       </c>
@@ -6335,7 +7805,6 @@
           <t>1/5/9/1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>6.6</v>
       </c>
@@ -6416,7 +7885,6 @@
           <t>6/2/2/3/4/4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>7</v>
       </c>
@@ -6497,7 +7965,6 @@
           <t>10/6/6/1/4/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5.48</v>
       </c>
@@ -6578,7 +8045,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5</v>
       </c>
@@ -6659,7 +8125,6 @@
           <t>8/2/8/12/7/1</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5</v>
       </c>
@@ -6740,7 +8205,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>5</v>
       </c>
@@ -6821,7 +8285,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>5</v>
       </c>
@@ -6902,7 +8365,6 @@
           <t>9/5/10/9</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.3</v>
       </c>
@@ -7114,7 +8576,6 @@
           <t>1/3/4/6/1/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.81</v>
       </c>
@@ -7195,7 +8656,6 @@
           <t>2/1/1/2/6/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.19</v>
       </c>
@@ -7276,7 +8736,6 @@
           <t>8/4/5/3/1/6</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.43</v>
       </c>
@@ -7357,7 +8816,6 @@
           <t>1/6/2/3/5/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>7.43</v>
       </c>
@@ -7438,7 +8896,6 @@
           <t>5/8/5/5/10/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.19</v>
       </c>
@@ -7519,7 +8976,6 @@
           <t>9/5/10/4/1/4</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.95</v>
       </c>
@@ -7600,7 +9056,6 @@
           <t>12/10/11/12/1/2</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5.43</v>
       </c>
@@ -7681,7 +9136,6 @@
           <t>3/2/1/2/11/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.9</v>
       </c>
@@ -7762,7 +9216,6 @@
           <t>6/4/7/9/7/4</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4</v>
       </c>
@@ -7843,7 +9296,6 @@
           <t>8/9/1/5/1/9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5.62</v>
       </c>
@@ -7924,7 +9376,6 @@
           <t>4/10/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.83</v>
       </c>
@@ -8005,7 +9456,6 @@
           <t>7/11/7/2/10/9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>3.19</v>
       </c>
@@ -8086,7 +9536,6 @@
           <t>10/5/9/9/8/11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1.95</v>
       </c>
@@ -8167,7 +9616,6 @@
           <t>2/4/12/13/14/14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1.86</v>
       </c>
@@ -8352,7 +9800,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>10</t>
@@ -8454,7 +9901,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>4</t>
@@ -8556,7 +10002,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>6</t>
@@ -8658,7 +10103,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>3</t>
@@ -8760,7 +10204,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>1</t>
@@ -8862,7 +10305,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>3</t>
@@ -8964,7 +10406,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>10</t>
@@ -9066,7 +10507,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
@@ -9168,7 +10608,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>7</t>
@@ -9270,7 +10709,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>1</t>
@@ -9372,7 +10810,6 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>6</t>
@@ -9647,7 +11084,6 @@
           <t>12/2/1/12/5/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.29</v>
       </c>
@@ -9728,7 +11164,6 @@
           <t>6/4/5/4/5/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.1</v>
       </c>
@@ -9809,7 +11244,6 @@
           <t>4/12/5/2/7/5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.95</v>
       </c>
@@ -9890,7 +11324,6 @@
           <t>8/6/4/10/5/8</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>3.29</v>
       </c>
@@ -9971,7 +11404,6 @@
           <t>2/7/4/9/4/12</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.67</v>
       </c>
@@ -10052,7 +11484,6 @@
           <t>1/3/3/9/10/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.14</v>
       </c>
@@ -10133,7 +11564,6 @@
           <t>6/13/12/9/8/5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.71</v>
       </c>
@@ -10214,7 +11644,6 @@
           <t>8/1/9/9/8/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.48</v>
       </c>
@@ -10295,7 +11724,6 @@
           <t>10/4/7/9/12/14</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.95</v>
       </c>
@@ -10376,7 +11804,6 @@
           <t>14/10/7/7/10/9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.95</v>
       </c>
@@ -10457,7 +11884,6 @@
           <t>12/11/3/7/5/13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>3.33</v>
       </c>
@@ -10538,7 +11964,6 @@
           <t>11/5/13/13/9/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.62</v>
       </c>
@@ -10619,7 +12044,6 @@
           <t>7/12/12/5/11/9</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.14</v>
       </c>
@@ -10700,7 +12124,6 @@
           <t>11/10/12/9/11/9</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1.48</v>
       </c>
@@ -10912,7 +12335,6 @@
           <t>14/2/2/1/5/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.57</v>
       </c>
@@ -10993,7 +12415,6 @@
           <t>10/14/1/2/1/8</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.24</v>
       </c>
@@ -11074,7 +12495,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -11155,7 +12575,6 @@
           <t>2/3/1/2/6/9</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.86</v>
       </c>
@@ -11236,7 +12655,6 @@
           <t>3/11/3/9/5/5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.62</v>
       </c>
@@ -11317,7 +12735,6 @@
           <t>8/3/8</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4</v>
       </c>
@@ -11398,7 +12815,6 @@
           <t>4/6/7/4/3/12</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.43</v>
       </c>
@@ -11479,7 +12895,6 @@
           <t>3/10/5/6/4/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.67</v>
       </c>
@@ -11560,7 +12975,6 @@
           <t>10/9/9/13</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.5</v>
       </c>
@@ -11641,7 +13055,6 @@
           <t>10/11/11/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1</v>
       </c>
@@ -11722,7 +13135,6 @@
           <t>13/11/11/10/11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -11803,7 +13215,6 @@
           <t>12/10/10/8</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.4</v>
       </c>
@@ -11884,7 +13295,6 @@
           <t>13/11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1</v>
       </c>
@@ -11965,7 +13375,6 @@
           <t>6/2/13/7/11/11</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2.29</v>
       </c>
@@ -12177,7 +13586,6 @@
           <t>1/1/3/3/2/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.81</v>
       </c>
@@ -12258,7 +13666,6 @@
           <t>3/10/6/9/1/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.67</v>
       </c>
@@ -12339,7 +13746,6 @@
           <t>2/5/9/1/5/3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.57</v>
       </c>
@@ -12420,7 +13826,6 @@
           <t>7/1/12/4/7/3</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.38</v>
       </c>
@@ -12501,7 +13906,6 @@
           <t>2/4/4/5/4/8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.81</v>
       </c>
@@ -12582,7 +13986,6 @@
           <t>8/3/2/6/4/11</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.62</v>
       </c>
@@ -12663,7 +14066,6 @@
           <t>9/5/6/9/10/6</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.9</v>
       </c>
@@ -12744,7 +14146,6 @@
           <t>11/10/8/13/3/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.67</v>
       </c>
@@ -12825,7 +14226,6 @@
           <t>9/12/8/4/13/13</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.14</v>
       </c>
@@ -12906,7 +14306,6 @@
           <t>13/9/11/14/14/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
@@ -13072,7 +14471,6 @@
           <t>13/9/11/12/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.13</v>
       </c>
@@ -13284,7 +14682,6 @@
           <t>6/1/11/6/2/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.05</v>
       </c>
@@ -13365,7 +14762,6 @@
           <t>3/2/1/3/3/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>8.380000000000001</v>
       </c>
@@ -13446,7 +14842,6 @@
           <t>8/4/10/3/4/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.62</v>
       </c>
@@ -13527,7 +14922,6 @@
           <t>13/1/9/8/3/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.43</v>
       </c>
@@ -13608,7 +15002,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -13689,7 +15082,6 @@
           <t>10/5/2/6/7/11</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.57</v>
       </c>
@@ -13770,7 +15162,6 @@
           <t>3/6/5/4/2/10</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5.05</v>
       </c>
@@ -13851,7 +15242,6 @@
           <t>8/5/5/5/10/14</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.76</v>
       </c>
@@ -13932,7 +15322,6 @@
           <t>9/7/4/9/8/8</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.67</v>
       </c>
@@ -14144,7 +15533,6 @@
           <t>7/3/2/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.6</v>
       </c>
@@ -14225,7 +15613,6 @@
           <t>8/3/5/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.3</v>
       </c>
@@ -14306,7 +15693,6 @@
           <t>4/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>8</v>
       </c>
@@ -14387,7 +15773,6 @@
           <t>1/2/10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.17</v>
       </c>
@@ -14468,7 +15853,6 @@
           <t>4/1/4/8/6/9</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4</v>
       </c>
@@ -14549,7 +15933,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -14630,7 +16013,6 @@
           <t>6/12/12/8/1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.47</v>
       </c>
@@ -14711,7 +16093,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
@@ -14792,7 +16173,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5</v>
       </c>
@@ -14873,7 +16253,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5</v>
       </c>
@@ -14954,7 +16333,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>5</v>
       </c>
@@ -15035,7 +16413,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>5</v>
       </c>
@@ -15116,7 +16493,6 @@
           <t>2/12/7/4</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>4.4</v>
       </c>
@@ -15197,7 +16573,6 @@
           <t>6/10/7/9/9/8</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2.14</v>
       </c>
@@ -15409,7 +16784,6 @@
           <t>1/2/3/1/4/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.380000000000001</v>
       </c>
@@ -15490,7 +16864,6 @@
           <t>10/4/3/5/1/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.38</v>
       </c>
@@ -15571,7 +16944,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -15652,7 +17024,6 @@
           <t>9/6/5/3/10/7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>3.81</v>
       </c>
@@ -15733,7 +17104,6 @@
           <t>3/11/6/3/7/4</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -15814,7 +17184,6 @@
           <t>6/1/6/12/5/9</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.67</v>
       </c>
@@ -15895,7 +17264,6 @@
           <t>5/4/6/7/8/7</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.29</v>
       </c>
@@ -15976,7 +17344,6 @@
           <t>7/12/12/14</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1.2</v>
       </c>
@@ -16057,7 +17424,6 @@
           <t>11/9/7/4/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.87</v>
       </c>
@@ -16138,7 +17504,6 @@
           <t>4/5/12/8/12/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.81</v>
       </c>
@@ -16219,7 +17584,6 @@
           <t>7/11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.67</v>
       </c>
@@ -16300,7 +17664,6 @@
           <t>12/9/14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.33</v>
       </c>
@@ -16381,7 +17744,6 @@
           <t>12/12/11/11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1</v>
       </c>
@@ -16462,7 +17824,6 @@
           <t>13/10/10/12</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1</v>
       </c>
@@ -16674,7 +18035,6 @@
           <t>9/3/4/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.8</v>
       </c>
@@ -16755,7 +18115,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5</v>
       </c>
@@ -16836,7 +18195,6 @@
           <t>7/4/8/3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.3</v>
       </c>
@@ -16917,7 +18275,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -16998,7 +18355,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -17079,7 +18435,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -17160,7 +18515,6 @@
           <t>9/8/1/11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4</v>
       </c>
@@ -17241,7 +18595,6 @@
           <t>1/6/3/5/5/10</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.43</v>
       </c>
@@ -17322,7 +18675,6 @@
           <t>14/10/2/6/6/9</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.71</v>
       </c>
@@ -17403,7 +18755,6 @@
           <t>4/4/12/4/5/3</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5.62</v>
       </c>
@@ -17484,7 +18835,6 @@
           <t>6/10/3/9/12/7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.9</v>
       </c>
@@ -17565,7 +18915,6 @@
           <t>13/14/13/12/13</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1</v>
       </c>
@@ -17646,7 +18995,6 @@
           <t>9/10/10/11/11/6</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1.9</v>
       </c>
@@ -17727,7 +19075,6 @@
           <t>10/11/12/13/12</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1</v>
       </c>
